--- a/artfynd/A 33388-2025 artfynd.xlsx
+++ b/artfynd/A 33388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,6 +1795,297 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126421056</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hungsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>558981</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6986390</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126421057</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hungsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>558857</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6986110</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126421055</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hungsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558945</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6986433</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33388-2025 artfynd.xlsx
+++ b/artfynd/A 33388-2025 artfynd.xlsx
@@ -1797,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126421056</v>
+        <v>126421057</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>91260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558981</v>
+        <v>558857</v>
       </c>
       <c r="R13" t="n">
-        <v>6986390</v>
+        <v>6986110</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,32 +1894,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126421057</v>
+        <v>126421056</v>
       </c>
       <c r="B14" t="n">
-        <v>91260</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558857</v>
+        <v>558981</v>
       </c>
       <c r="R14" t="n">
-        <v>6986110</v>
+        <v>6986390</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 33388-2025 artfynd.xlsx
+++ b/artfynd/A 33388-2025 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>126421057</v>
       </c>
       <c r="B13" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>126421056</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>126421055</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33388-2025 artfynd.xlsx
+++ b/artfynd/A 33388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118505487</v>
+        <v>118505485</v>
       </c>
       <c r="B2" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558839</v>
+        <v>558980</v>
       </c>
       <c r="R2" t="n">
-        <v>6986038</v>
+        <v>6986002</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118505540</v>
+        <v>118505525</v>
       </c>
       <c r="B3" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558996</v>
+        <v>558839</v>
       </c>
       <c r="R3" t="n">
-        <v>6986391</v>
+        <v>6986038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,12 +872,7 @@
         <v>118505526</v>
       </c>
       <c r="B4" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,12 +889,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118505578</v>
+        <v>118505527</v>
       </c>
       <c r="B5" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558770</v>
+        <v>559046</v>
       </c>
       <c r="R5" t="n">
-        <v>6986267</v>
+        <v>6986023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118505521</v>
+        <v>118505487</v>
       </c>
       <c r="B6" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558823</v>
+        <v>558839</v>
       </c>
       <c r="R6" t="n">
-        <v>6986020</v>
+        <v>6986038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118505550</v>
+        <v>118505489</v>
       </c>
       <c r="B7" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558825</v>
+        <v>559046</v>
       </c>
       <c r="R7" t="n">
-        <v>6986050</v>
+        <v>6986023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504896</v>
+        <v>118505578</v>
       </c>
       <c r="B8" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558769</v>
+        <v>558770</v>
       </c>
       <c r="R8" t="n">
-        <v>6986354</v>
+        <v>6986267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118505548</v>
+        <v>118505521</v>
       </c>
       <c r="B9" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558857</v>
+        <v>558823</v>
       </c>
       <c r="R9" t="n">
-        <v>6986202</v>
+        <v>6986020</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118505547</v>
+        <v>118504896</v>
       </c>
       <c r="B10" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558839</v>
+        <v>558769</v>
       </c>
       <c r="R10" t="n">
-        <v>6986233</v>
+        <v>6986354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118505525</v>
+        <v>118505540</v>
       </c>
       <c r="B11" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558839</v>
+        <v>558996</v>
       </c>
       <c r="R11" t="n">
-        <v>6986038</v>
+        <v>6986391</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118505509</v>
+        <v>118505547</v>
       </c>
       <c r="B12" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559050</v>
+        <v>558839</v>
       </c>
       <c r="R12" t="n">
-        <v>6985911</v>
+        <v>6986233</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126421057</v>
+        <v>118505548</v>
       </c>
       <c r="B13" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hungsjöberget, Jmt</t>
+          <t>Hungsjöbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>558857</v>
       </c>
       <c r="R13" t="n">
-        <v>6986110</v>
+        <v>6986202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,57 +1827,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126421056</v>
+        <v>118505550</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hungsjöberget, Jmt</t>
+          <t>Hungsjöbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558981</v>
+        <v>558825</v>
       </c>
       <c r="R14" t="n">
-        <v>6986390</v>
+        <v>6986050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1979,57 +1924,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126421055</v>
+        <v>118505556</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hungsjöberget, Jmt</t>
+          <t>Hungsjöbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558945</v>
+        <v>559017</v>
       </c>
       <c r="R15" t="n">
-        <v>6986433</v>
+        <v>6986005</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,15 +2021,403 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118505528</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hungsjöbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558991</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6986003</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126421055</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hungsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558945</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6986433</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126421056</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hungsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558981</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6986390</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118505509</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hungsjöbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>559050</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6985911</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33388-2025 artfynd.xlsx
+++ b/artfynd/A 33388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505525</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505526</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505527</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505487</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505489</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505578</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505521</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504896</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505540</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505547</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505548</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505550</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505556</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505528</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126421055</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126421056</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,8 +2508,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505509</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>